--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3465-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3465-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AA399A2-C387-4F6B-9B91-DF5AC6E0FBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31EC2DB9-0F21-4FF0-B364-5B81F984A112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BC485127-407A-4EA1-8465-434FB26CC04C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{80B14932-6D12-486C-9180-088AAA3DA1A0}"/>
   </bookViews>
   <sheets>
     <sheet name="3465-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1475,26 +1475,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4F4131-8436-435D-8F05-C50E6EEE5756}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2B2123-18E0-4DBF-99F2-D90118D3F580}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1684,7 +1684,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2023</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2022</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2021</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2020</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>29</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2019</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2018</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2017</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2016</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2015</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2014</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2013</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2012</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2011</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>2010</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>2009</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>2008</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>2007</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>2006</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>2005</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>2004</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>46</v>
       </c>
